--- a/Active May.xlsx
+++ b/Active May.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12300" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23256" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Voda" sheetId="1" r:id="rId1"/>
@@ -135,14 +135,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,152 +167,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,204 +183,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -553,251 +217,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -836,89 +258,158 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -929,7 +420,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -957,149 +448,32 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1362,17 +736,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.7142857142857" customWidth="1"/>
-    <col min="2" max="3" width="7.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="3" width="7.109375" customWidth="1"/>
     <col min="4" max="4" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1641,18 +1015,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.7142857142857" customWidth="1"/>
-    <col min="2" max="3" width="7.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="3" width="7.109375" customWidth="1"/>
     <col min="4" max="4" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1830,6 +1202,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Active May.xlsx
+++ b/Active May.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Voda!$A$1:$D$17</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>sara</t>
+  </si>
+  <si>
+    <t>ahmed</t>
   </si>
 </sst>
 </file>
@@ -194,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -217,13 +220,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -255,6 +269,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -742,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -1012,6 +1032,20 @@
         <v>1</v>
       </c>
       <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="12">
+        <v>100</v>
+      </c>
+      <c r="C18" s="12">
+        <v>70</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Active May.xlsx
+++ b/Active May.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23256" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23256" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Voda" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>Name</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Asmaa</t>
   </si>
   <si>
-    <t>Malak</t>
-  </si>
-  <si>
     <t>Aya Ahmed</t>
   </si>
   <si>
@@ -132,7 +129,7 @@
     <t>sara</t>
   </si>
   <si>
-    <t>ahmed</t>
+    <t>Ahmed</t>
   </si>
 </sst>
 </file>
@@ -197,7 +194,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -220,24 +217,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -269,12 +255,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -762,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -827,7 +807,7 @@
         <v>40</v>
       </c>
       <c r="C4" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D4" s="8">
         <v>6</v>
@@ -898,13 +878,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B9" s="4">
         <v>35</v>
       </c>
       <c r="C9" s="4">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D9" s="8">
         <v>5</v>
@@ -913,7 +893,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <v>35</v>
@@ -928,7 +908,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <v>42</v>
@@ -943,7 +923,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <v>30</v>
@@ -958,7 +938,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <v>40</v>
@@ -975,7 +955,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <v>30</v>
@@ -990,7 +970,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="8">
         <v>30</v>
@@ -1005,7 +985,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="8">
         <v>30</v>
@@ -1020,7 +1000,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <v>35</v>
@@ -1032,20 +1012,6 @@
         <v>1</v>
       </c>
       <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="12">
-        <v>100</v>
-      </c>
-      <c r="C18" s="12">
-        <v>70</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1078,23 +1044,23 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="C2" s="4">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4">
         <v>3</v>
@@ -1106,10 +1072,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4">
         <v>4</v>
@@ -1121,10 +1087,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
@@ -1134,10 +1100,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4">
         <v>4</v>
@@ -1149,10 +1115,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="4">
         <v>5</v>
@@ -1161,15 +1127,15 @@
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4">
         <v>9</v>
@@ -1181,10 +1147,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4">
         <v>2</v>
@@ -1193,15 +1159,15 @@
         <v>8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4">
         <v>2</v>
@@ -1210,7 +1176,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5">
